--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_23.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_23.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SelfConfidence</t>
+          <t>Musician?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Happiness</t>
+          <t>IV</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-1.144549196236823</v>
+        <v>0.1183253129175063</v>
       </c>
       <c r="C2">
-        <v>-2.132607636587338</v>
+        <v>-0.08434640076117773</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.7771450558546225</v>
+        <v>-0.5651029419206718</v>
       </c>
       <c r="C3">
-        <v>-0.4121247829643349</v>
+        <v>-0.9545228307715672</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.650118109988056</v>
+        <v>-1.429168775337694</v>
       </c>
       <c r="C4">
-        <v>0.1956614896073196</v>
+        <v>-2.197833166908133</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.74392434282379</v>
+        <v>2.9480452379001</v>
       </c>
       <c r="C5">
-        <v>0.8629352827120644</v>
+        <v>1.823106548646546</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.220216497620272</v>
+        <v>-0.2035903567906266</v>
       </c>
       <c r="C6">
-        <v>0.1849523306859563</v>
+        <v>0.2598745105269362</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.7216405026446742</v>
+        <v>0.530721289342575</v>
       </c>
       <c r="C7">
-        <v>0.758520054539081</v>
+        <v>-0.0776574184582719</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.9734508347625842</v>
+        <v>1.192404788187762</v>
       </c>
       <c r="C8">
-        <v>-1.78507827481313</v>
+        <v>1.261121382297418</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.8918337306951081</v>
+        <v>1.068950315741311</v>
       </c>
       <c r="C9">
-        <v>0.439099562140622</v>
+        <v>-0.004209799241650825</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.9386738955298335</v>
+        <v>0.4733725240103402</v>
       </c>
       <c r="C10">
-        <v>0.09533072549189286</v>
+        <v>0.8018233900885188</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.547506976060103</v>
+        <v>-0.3887095508158951</v>
       </c>
       <c r="C11">
-        <v>0.006469437553981883</v>
+        <v>-1.697596852254867</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.04623244664539649</v>
+        <v>-0.1019690566820512</v>
       </c>
       <c r="C12">
-        <v>0.7315179127697472</v>
+        <v>-0.8762397723434165</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.085819357770341</v>
+        <v>0.4352869618003282</v>
       </c>
       <c r="C13">
-        <v>0.8008215363641739</v>
+        <v>-0.2103711752702227</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.3081832554282727</v>
+        <v>-0.7716304020170555</v>
       </c>
       <c r="C14">
-        <v>-1.023622262017051</v>
+        <v>-0.02179680562123998</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.2450697144989426</v>
+        <v>-1.549102046876338</v>
       </c>
       <c r="C15">
-        <v>-0.142732203990867</v>
+        <v>0.9460534920316868</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.9295438667225494</v>
+        <v>-0.7742509292769854</v>
       </c>
       <c r="C16">
-        <v>-0.6847611462485944</v>
+        <v>0.6549307310885226</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.4143636387197057</v>
+        <v>1.56146829753262</v>
       </c>
       <c r="C17">
-        <v>-0.6932261381396132</v>
+        <v>-0.01848419532562762</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.01842207227447</v>
+        <v>-0.5491319996885214</v>
       </c>
       <c r="C18">
-        <v>0.3536988071891112</v>
+        <v>1.068101115501891</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.1980358894267223</v>
+        <v>-0.166947619124014</v>
       </c>
       <c r="C19">
-        <v>1.123232133239652</v>
+        <v>-1.007253176087038</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.4471853338924491</v>
+        <v>-0.4050841922782353</v>
       </c>
       <c r="C20">
-        <v>-0.06409796587794617</v>
+        <v>0.6727842040176452</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.2613630105225961</v>
+        <v>-2.168706934906114</v>
       </c>
       <c r="C21">
-        <v>-0.6122017200328693</v>
+        <v>-0.199769744573543</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.05932624799665043</v>
+        <v>-2.521327764673373</v>
       </c>
       <c r="C22">
-        <v>-0.3500914013450917</v>
+        <v>-1.436343027432044</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.7656537025184404</v>
+        <v>-0.8313203579655233</v>
       </c>
       <c r="C23">
-        <v>1.240522312234192</v>
+        <v>0.1769234221696276</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.1049904074379182</v>
+        <v>-3.318666437955878</v>
       </c>
       <c r="C24">
-        <v>-0.1434216890698174</v>
+        <v>-0.9283014451513236</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.5109667064642982</v>
+        <v>-1.626099467107816</v>
       </c>
       <c r="C25">
-        <v>-2.66491118740546</v>
+        <v>-0.6140185794842993</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.3591859421071545</v>
+        <v>1.258068626051285</v>
       </c>
       <c r="C26">
-        <v>0.6215063509402976</v>
+        <v>2.038679684825857</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.4161632927608172</v>
+        <v>0.707940798375399</v>
       </c>
       <c r="C27">
-        <v>0.3739894636544437</v>
+        <v>-0.5400054474551759</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.559563226578757</v>
+        <v>-0.5155986235471632</v>
       </c>
       <c r="C28">
-        <v>1.323081549625278</v>
+        <v>-1.591729826048793</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.3306270779483484</v>
+        <v>1.91822570541266</v>
       </c>
       <c r="C29">
-        <v>-0.7914008593894672</v>
+        <v>-0.2540595712250491</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.2044667953701511</v>
+        <v>0.1362020205004862</v>
       </c>
       <c r="C30">
-        <v>0.5479073372480439</v>
+        <v>0.9682761380604461</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.4120133928191987</v>
+        <v>-0.6408596682021164</v>
       </c>
       <c r="C31">
-        <v>0.9579585594069699</v>
+        <v>-0.3346910125419258</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.4940707337295732</v>
+        <v>0.3790275422756226</v>
       </c>
       <c r="C32">
-        <v>-1.252427970549178</v>
+        <v>-0.2183834361365913</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.600126758272284</v>
+        <v>-1.482509151560823</v>
       </c>
       <c r="C33">
-        <v>1.672938099457356</v>
+        <v>1.362855191239358</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.2254489892815408</v>
+        <v>1.80058355355335</v>
       </c>
       <c r="C34">
-        <v>-0.8984520221612775</v>
+        <v>1.580622539459295</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.4170561585577789</v>
+        <v>-0.4672880499294888</v>
       </c>
       <c r="C35">
-        <v>-0.4062254006313831</v>
+        <v>-0.10188747599661</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.3558562093045803</v>
+        <v>-0.37860943344704</v>
       </c>
       <c r="C36">
-        <v>1.977001255098481</v>
+        <v>-1.412465091378108</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-1.537958895347045</v>
+        <v>-0.03888216983731596</v>
       </c>
       <c r="C37">
-        <v>-0.9105266896340066</v>
+        <v>-0.6652602905974726</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.3550944619191274</v>
+        <v>-1.239776291687834</v>
       </c>
       <c r="C38">
-        <v>0.66131822598495</v>
+        <v>-0.3323596347535423</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.4037208973021603</v>
+        <v>-0.3168132784192871</v>
       </c>
       <c r="C39">
-        <v>-0.7432493437792408</v>
+        <v>1.71755418167044</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.6041950570699539</v>
+        <v>-0.366340591950615</v>
       </c>
       <c r="C40">
-        <v>-1.207947165091298</v>
+        <v>-1.043012250551391</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.6212898565872269</v>
+        <v>1.345375568499113</v>
       </c>
       <c r="C41">
-        <v>0.746255827778722</v>
+        <v>0.6530297264509318</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.5665119523110829</v>
+        <v>1.255148880288446</v>
       </c>
       <c r="C42">
-        <v>0.2094424893340939</v>
+        <v>-0.1266289193361038</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.6419675186159914</v>
+        <v>1.395305470812188</v>
       </c>
       <c r="C43">
-        <v>0.762177781544174</v>
+        <v>0.8498801526618881</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>2.420462099192259</v>
+        <v>1.394605426587134</v>
       </c>
       <c r="C44">
-        <v>1.161621075756081</v>
+        <v>1.791496960002575</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>1.079959897193506</v>
+        <v>-0.1439747494912874</v>
       </c>
       <c r="C45">
-        <v>0.9368267592254144</v>
+        <v>0.705101638716164</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.058323693624041</v>
+        <v>0.0465117562433001</v>
       </c>
       <c r="C46">
-        <v>0.119519375193781</v>
+        <v>-0.08948577239668142</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.3599000767764785</v>
+        <v>0.9083720981297722</v>
       </c>
       <c r="C47">
-        <v>0.07564964486282336</v>
+        <v>2.282937572564458</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-1.458580225674664</v>
+        <v>0.0486719764536346</v>
       </c>
       <c r="C48">
-        <v>-1.597933504946072</v>
+        <v>-0.3492802508375836</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.786101644108419</v>
+        <v>0.06494712722641754</v>
       </c>
       <c r="C49">
-        <v>0.8748820444879593</v>
+        <v>1.059429525663852</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>1.88624445910034</v>
+        <v>-0.4130569364976763</v>
       </c>
       <c r="C50">
-        <v>1.518475504192541</v>
+        <v>-0.04774981809697236</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,1960 @@
         </is>
       </c>
       <c r="B51">
-        <v>1.061096561495294</v>
+        <v>1.554754899267212</v>
       </c>
       <c r="C51">
-        <v>1.127815717014914</v>
+        <v>0.05947220744507364</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.4775662465561328</v>
+      </c>
+      <c r="C52">
+        <v>-0.2025530021162809</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>-0.2172549285374725</v>
+      </c>
+      <c r="C53">
+        <v>-0.121000701964001</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>1.037737765126946</v>
+      </c>
+      <c r="C54">
+        <v>-0.2355538795186818</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>0.2625243418549397</v>
+      </c>
+      <c r="C55">
+        <v>0.003515877186013719</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>-0.7202963022055643</v>
+      </c>
+      <c r="C56">
+        <v>-0.6223034700430479</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>2.849775775166924</v>
+      </c>
+      <c r="C57">
+        <v>2.520656291696791</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>-0.6893071773948156</v>
+      </c>
+      <c r="C58">
+        <v>1.258363074801507</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>-0.1038658709712453</v>
+      </c>
+      <c r="C59">
+        <v>-1.213831987581784</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>0.1639879978313195</v>
+      </c>
+      <c r="C60">
+        <v>0.8783393874848191</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>-0.4336542301358364</v>
+      </c>
+      <c r="C61">
+        <v>0.3531573693599026</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>1.463037380216578</v>
+      </c>
+      <c r="C62">
+        <v>0.8926915655130325</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>0.6597096161554317</v>
+      </c>
+      <c r="C63">
+        <v>-0.3753798817242271</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>-0.2333604666196344</v>
+      </c>
+      <c r="C64">
+        <v>-0.1440819969922096</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>-1.219371470223892</v>
+      </c>
+      <c r="C65">
+        <v>-0.7097383279819129</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>2.525362061978316</v>
+      </c>
+      <c r="C66">
+        <v>0.8671549334732709</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>0.3162590328418385</v>
+      </c>
+      <c r="C67">
+        <v>0.6309313857693</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>1.321918363740143</v>
+      </c>
+      <c r="C68">
+        <v>0.2434677453888946</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>-1.751373064306249</v>
+      </c>
+      <c r="C69">
+        <v>-2.818877399892648</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>-0.3066855005944199</v>
+      </c>
+      <c r="C70">
+        <v>1.323415884924295</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>0.1603173413024678</v>
+      </c>
+      <c r="C71">
+        <v>-0.2841849229478279</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>-0.900648305851902</v>
+      </c>
+      <c r="C72">
+        <v>-0.102284087995283</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>-1.119301444220494</v>
+      </c>
+      <c r="C73">
+        <v>-0.3022954785829194</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>0.2485215125836702</v>
+      </c>
+      <c r="C74">
+        <v>-0.6811115072532377</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>0.334046019073077</v>
+      </c>
+      <c r="C75">
+        <v>-0.8791070847783258</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>0.3074825108399755</v>
+      </c>
+      <c r="C76">
+        <v>-0.1592074914490239</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>-0.6598581822482588</v>
+      </c>
+      <c r="C77">
+        <v>0.3064804663526017</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>1.108377463566107</v>
+      </c>
+      <c r="C78">
+        <v>0.2020624521364165</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>-1.404600906940467</v>
+      </c>
+      <c r="C79">
+        <v>-1.910543127610285</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>-1.008882741386608</v>
+      </c>
+      <c r="C80">
+        <v>1.434580010715243</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>-0.8063288969060992</v>
+      </c>
+      <c r="C81">
+        <v>0.3173169121159101</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>1.193490858729509</v>
+      </c>
+      <c r="C82">
+        <v>0.09475453373021941</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>-0.1101256968782641</v>
+      </c>
+      <c r="C83">
+        <v>-0.7707120784865682</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>-0.07251887518321087</v>
+      </c>
+      <c r="C84">
+        <v>-0.4682226998266257</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>-1.257219148833332</v>
+      </c>
+      <c r="C85">
+        <v>-0.6572872864855469</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>-0.7981756014725678</v>
+      </c>
+      <c r="C86">
+        <v>-2.033545352442758</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>-1.744898509658795</v>
+      </c>
+      <c r="C87">
+        <v>0.4650377573956438</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>0.2730497914822516</v>
+      </c>
+      <c r="C88">
+        <v>0.5843486945235932</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>-0.9107296119268945</v>
+      </c>
+      <c r="C89">
+        <v>-0.7753339886106845</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>0.7725801797772248</v>
+      </c>
+      <c r="C90">
+        <v>1.359070382361072</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>0.6796858433573105</v>
+      </c>
+      <c r="C91">
+        <v>0.8639747349718113</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>-1.060590850197247</v>
+      </c>
+      <c r="C92">
+        <v>-0.7631915628520135</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>1.225675176525021</v>
+      </c>
+      <c r="C93">
+        <v>1.025930475336431</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>1.30532757314367</v>
+      </c>
+      <c r="C94">
+        <v>0.2587546425474604</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>0.6138997834146827</v>
+      </c>
+      <c r="C95">
+        <v>1.258217287309839</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>0.4940022721826735</v>
+      </c>
+      <c r="C96">
+        <v>-0.4291982711359205</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>-0.7686993217580521</v>
+      </c>
+      <c r="C97">
+        <v>-0.2582639133818883</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>-0.2468553429507487</v>
+      </c>
+      <c r="C98">
+        <v>1.133687389147525</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>0.7050087681352132</v>
+      </c>
+      <c r="C99">
+        <v>0.6152052585956347</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>-0.1267045432428575</v>
+      </c>
+      <c r="C100">
+        <v>1.077672439786024</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>1.797391695998586</v>
+      </c>
+      <c r="C101">
+        <v>1.876661664683732</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>0.287126301140578</v>
+      </c>
+      <c r="C102">
+        <v>-0.4155682168380833</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>0.575565590347449</v>
+      </c>
+      <c r="C103">
+        <v>0.05528849350646456</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>-0.2214529923371802</v>
+      </c>
+      <c r="C104">
+        <v>-0.06203340200117649</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>-0.9459534893751811</v>
+      </c>
+      <c r="C105">
+        <v>-0.3373123891965555</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>-1.791029702410104</v>
+      </c>
+      <c r="C106">
+        <v>-1.097468806500171</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>0.1728703005146343</v>
+      </c>
+      <c r="C107">
+        <v>1.347230201295137</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>-0.2955493527929902</v>
+      </c>
+      <c r="C108">
+        <v>-0.01817525390314342</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>0.4768435355158026</v>
+      </c>
+      <c r="C109">
+        <v>0.6014493237064709</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-1.10839052266105</v>
+      </c>
+      <c r="C110">
+        <v>-0.7017596230256158</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>0.278497486184732</v>
+      </c>
+      <c r="C111">
+        <v>-0.7302905801944275</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.1609451777396868</v>
+      </c>
+      <c r="C112">
+        <v>-0.2717797995410801</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>-0.493207573166984</v>
+      </c>
+      <c r="C113">
+        <v>-2.063152317817382</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-1.559015180129124</v>
+      </c>
+      <c r="C114">
+        <v>-0.6593351789621278</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>-0.1864186655965854</v>
+      </c>
+      <c r="C115">
+        <v>-1.503843743560974</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>-0.8276820797535241</v>
+      </c>
+      <c r="C116">
+        <v>-0.2521685807556899</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>1.568339495231156</v>
+      </c>
+      <c r="C117">
+        <v>1.209129497251795</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>-0.9309527745144229</v>
+      </c>
+      <c r="C118">
+        <v>1.492653967060346</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>-0.4408757988162208</v>
+      </c>
+      <c r="C119">
+        <v>0.2555790186338152</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>-0.8943744382112059</v>
+      </c>
+      <c r="C120">
+        <v>-0.1761277736688052</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>-0.7254604212328301</v>
+      </c>
+      <c r="C121">
+        <v>-0.2785159598441637</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>0.1587749493064263</v>
+      </c>
+      <c r="C122">
+        <v>-0.2662857163233937</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>-1.690347864587675</v>
+      </c>
+      <c r="C123">
+        <v>-0.3579171245680861</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>2.014451719335001</v>
+      </c>
+      <c r="C124">
+        <v>0.4720258363712078</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>1.13825916139543</v>
+      </c>
+      <c r="C125">
+        <v>-0.3566761441443452</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>-0.2148903068276333</v>
+      </c>
+      <c r="C126">
+        <v>0.1059877574429286</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>0.2652948031106048</v>
+      </c>
+      <c r="C127">
+        <v>-0.8612862562128506</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-2.033438370618221</v>
+      </c>
+      <c r="C128">
+        <v>0.5290205522503467</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>0.1192836718704342</v>
+      </c>
+      <c r="C129">
+        <v>0.1514233186164413</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>0.8457159252479564</v>
+      </c>
+      <c r="C130">
+        <v>-0.561872114957223</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>-0.3180160023262178</v>
+      </c>
+      <c r="C131">
+        <v>0.3974848103861596</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>0.3072307910777262</v>
+      </c>
+      <c r="C132">
+        <v>-0.5419024080308583</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.2072391573222298</v>
+      </c>
+      <c r="C133">
+        <v>0.21219835230965</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>1.629676398748067</v>
+      </c>
+      <c r="C134">
+        <v>0.05914730211864172</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>0.3236537103331706</v>
+      </c>
+      <c r="C135">
+        <v>0.8459788243945973</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>-1.505721436144538</v>
+      </c>
+      <c r="C136">
+        <v>-1.321857017224218</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>-0.9942037208722635</v>
+      </c>
+      <c r="C137">
+        <v>0.577427117989358</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>0.4606470276981612</v>
+      </c>
+      <c r="C138">
+        <v>-0.9777844429829481</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>1.506753829244712</v>
+      </c>
+      <c r="C139">
+        <v>-0.5997820813858399</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>-0.65943598788005</v>
+      </c>
+      <c r="C140">
+        <v>-1.648789520332765</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>1.071822248840708</v>
+      </c>
+      <c r="C141">
+        <v>0.2058930208675883</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>-0.459310038358735</v>
+      </c>
+      <c r="C142">
+        <v>0.6147428602698044</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>-1.4457974162556</v>
+      </c>
+      <c r="C143">
+        <v>-0.3948887993511311</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>-1.039128875664222</v>
+      </c>
+      <c r="C144">
+        <v>0.1320539874716695</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>0.3469744154855171</v>
+      </c>
+      <c r="C145">
+        <v>0.5144124976754388</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>0.8331598038092579</v>
+      </c>
+      <c r="C146">
+        <v>-0.08985082021293933</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-0.2984887083939605</v>
+      </c>
+      <c r="C147">
+        <v>1.070334198903571</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>1.478855150475135</v>
+      </c>
+      <c r="C148">
+        <v>0.5985055360129827</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>1.350341900301768</v>
+      </c>
+      <c r="C149">
+        <v>0.6221351786477682</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>-0.9155717936188263</v>
+      </c>
+      <c r="C150">
+        <v>-0.1741621934681491</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>0.3805595353408457</v>
+      </c>
+      <c r="C151">
+        <v>-0.4005401875451899</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>0.4475280826644248</v>
+      </c>
+      <c r="C152">
+        <v>-0.09038128399583911</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>0.2587087671972292</v>
+      </c>
+      <c r="C153">
+        <v>0.4928422707757321</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>1.683269084827286</v>
+      </c>
+      <c r="C154">
+        <v>-1.286349211794887</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>0.6422831281907082</v>
+      </c>
+      <c r="C155">
+        <v>-0.2616461679839512</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>0.2366418742350226</v>
+      </c>
+      <c r="C156">
+        <v>0.1762095768886544</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>-0.320288083918818</v>
+      </c>
+      <c r="C157">
+        <v>-0.6353619669614832</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>-2.586852812107959</v>
+      </c>
+      <c r="C158">
+        <v>-1.540983302662034</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>-0.5266087737891367</v>
+      </c>
+      <c r="C159">
+        <v>-0.1380010714008453</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>1.594554730540228</v>
+      </c>
+      <c r="C160">
+        <v>-0.4257001701730394</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>0.4592852292682946</v>
+      </c>
+      <c r="C161">
+        <v>-0.9734828864262606</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>-0.8188530592176178</v>
+      </c>
+      <c r="C162">
+        <v>-0.19838000843272</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>-2.336293895004094</v>
+      </c>
+      <c r="C163">
+        <v>-0.8548280100571912</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>-1.114965035071881</v>
+      </c>
+      <c r="C164">
+        <v>0.8072459074416781</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>1.939863576233699</v>
+      </c>
+      <c r="C165">
+        <v>-0.1678765303881843</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>0.3164863811574104</v>
+      </c>
+      <c r="C166">
+        <v>0.211865232976941</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>1.388511890965089</v>
+      </c>
+      <c r="C167">
+        <v>-0.2020125189732153</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>1.307056633972032</v>
+      </c>
+      <c r="C168">
+        <v>1.634718301877791</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>0.3231143736839522</v>
+      </c>
+      <c r="C169">
+        <v>0.0296620914963998</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>-0.5699940714578557</v>
+      </c>
+      <c r="C170">
+        <v>-0.7320551352110489</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>-2.008022586347408</v>
+      </c>
+      <c r="C171">
+        <v>0.3399674481101232</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>0.2489821044870522</v>
+      </c>
+      <c r="C172">
+        <v>0.2220336926480456</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>-0.5139765328096044</v>
+      </c>
+      <c r="C173">
+        <v>2.489117791411302</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>-0.3554333121100716</v>
+      </c>
+      <c r="C174">
+        <v>0.472005108864901</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>-1.65842353261955</v>
+      </c>
+      <c r="C175">
+        <v>-0.9660643857879254</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>-1.347365371830497</v>
+      </c>
+      <c r="C176">
+        <v>-1.457657167322526</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>-1.573587138598674</v>
+      </c>
+      <c r="C177">
+        <v>0.3477459428378579</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>-1.77877938563325</v>
+      </c>
+      <c r="C178">
+        <v>-0.6241105296598941</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>2.315638853630976</v>
+      </c>
+      <c r="C179">
+        <v>1.919995531294454</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>0.6454890222425421</v>
+      </c>
+      <c r="C180">
+        <v>1.403561205939294</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>0.996441720095682</v>
+      </c>
+      <c r="C181">
+        <v>1.428931645350553</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>1.596426391458911</v>
+      </c>
+      <c r="C182">
+        <v>0.1137062892882119</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>-0.1581869566876613</v>
+      </c>
+      <c r="C183">
+        <v>1.196382278626211</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>-0.7265264141953062</v>
+      </c>
+      <c r="C184">
+        <v>-0.4092859092883339</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>0.8169856774268668</v>
+      </c>
+      <c r="C185">
+        <v>1.863879211795322</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>1.128003999066118</v>
+      </c>
+      <c r="C186">
+        <v>-1.503333443698705</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-0.9153350559483864</v>
+      </c>
+      <c r="C187">
+        <v>-0.8259794791526769</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>-1.219235757309374</v>
+      </c>
+      <c r="C188">
+        <v>1.883591939194525</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>-0.4166230128906609</v>
+      </c>
+      <c r="C189">
+        <v>0.5805921691833805</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>1.421174013529506</v>
+      </c>
+      <c r="C190">
+        <v>-0.3109349394481958</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>-0.06350975662507889</v>
+      </c>
+      <c r="C191">
+        <v>0.08639546984661409</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>0.5084848179857847</v>
+      </c>
+      <c r="C192">
+        <v>-0.3582878491232462</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>-0.6057315931475918</v>
+      </c>
+      <c r="C193">
+        <v>-0.5328784527417578</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>-1.198166605027221</v>
+      </c>
+      <c r="C194">
+        <v>-0.5112968551755055</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>-1.203943044212335</v>
+      </c>
+      <c r="C195">
+        <v>-2.033223106769248</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>-0.6866737229160604</v>
+      </c>
+      <c r="C196">
+        <v>1.044930375126655</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>1.745764354631904</v>
+      </c>
+      <c r="C197">
+        <v>0.8129758802569539</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>1.351596773583035</v>
+      </c>
+      <c r="C198">
+        <v>0.9253050871299663</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>-0.8137513558427263</v>
+      </c>
+      <c r="C199">
+        <v>-1.00806339678082</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>0.5975841533631649</v>
+      </c>
+      <c r="C200">
+        <v>2.422979846556268</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>1.44532916308563</v>
+      </c>
+      <c r="C201">
+        <v>0.2484392239711448</v>
       </c>
     </row>
   </sheetData>
